--- a/total_parcelas.xlsx
+++ b/total_parcelas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3097C65D-5068-433C-BBEA-4D02D09598B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6406CAA5-A9A8-4C66-B0F9-512E34AFF4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{326D8460-CF33-46E7-A7F9-8315620B1DD2}"/>
   </bookViews>
@@ -523,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE44BCBA-D928-4EB0-BB70-EF020CEEAF2E}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -568,8 +568,8 @@
       <c r="E2" s="2">
         <v>14.86</v>
       </c>
-      <c r="F2" s="1">
-        <v>18</v>
+      <c r="F2" s="2">
+        <v>0.18</v>
       </c>
       <c r="G2" s="2">
         <v>1.4339999999999999</v>
@@ -594,8 +594,8 @@
       <c r="E3" s="2">
         <v>10.393333333333333</v>
       </c>
-      <c r="F3" s="1">
-        <v>34</v>
+      <c r="F3" s="2">
+        <v>0.34</v>
       </c>
       <c r="G3" s="2">
         <v>2.254</v>
@@ -620,8 +620,8 @@
       <c r="E4" s="2">
         <v>16.02</v>
       </c>
-      <c r="F4" s="1">
-        <v>20.6</v>
+      <c r="F4" s="2">
+        <v>0.20600000000000002</v>
       </c>
       <c r="G4" s="2">
         <v>2.0140000000000002</v>
@@ -646,8 +646,8 @@
       <c r="E5" s="2">
         <v>20.04</v>
       </c>
-      <c r="F5" s="1">
-        <v>34</v>
+      <c r="F5" s="2">
+        <v>0.34</v>
       </c>
       <c r="G5" s="2">
         <v>2.742</v>
@@ -672,8 +672,8 @@
       <c r="E6" s="2">
         <v>11.04</v>
       </c>
-      <c r="F6" s="1">
-        <v>22.2</v>
+      <c r="F6" s="2">
+        <v>0.222</v>
       </c>
       <c r="G6" s="2">
         <v>1.21</v>
@@ -698,8 +698,8 @@
       <c r="E7" s="2">
         <v>9.36</v>
       </c>
-      <c r="F7" s="1">
-        <v>22.2</v>
+      <c r="F7" s="2">
+        <v>0.222</v>
       </c>
       <c r="G7" s="2">
         <v>1.5779999999999998</v>
@@ -724,8 +724,8 @@
       <c r="E8" s="2">
         <v>9.125</v>
       </c>
-      <c r="F8" s="1">
-        <v>15.5</v>
+      <c r="F8" s="2">
+        <v>0.155</v>
       </c>
       <c r="G8" s="2">
         <v>1.7674999999999998</v>
@@ -750,8 +750,8 @@
       <c r="E9" s="2">
         <v>8.16</v>
       </c>
-      <c r="F9" s="1">
-        <v>28.2</v>
+      <c r="F9" s="2">
+        <v>0.28199999999999997</v>
       </c>
       <c r="G9" s="2">
         <v>1.92</v>
@@ -776,8 +776,8 @@
       <c r="E10" s="2">
         <v>10.074999999999999</v>
       </c>
-      <c r="F10" s="1">
-        <v>34.25</v>
+      <c r="F10" s="2">
+        <v>0.34250000000000003</v>
       </c>
       <c r="G10" s="2">
         <v>2.1124999999999998</v>
@@ -802,8 +802,8 @@
       <c r="E11" s="2">
         <v>6.3999999999999995</v>
       </c>
-      <c r="F11" s="1">
-        <v>33</v>
+      <c r="F11" s="2">
+        <v>0.33</v>
       </c>
       <c r="G11" s="2">
         <v>2.4500000000000002</v>
@@ -828,8 +828,8 @@
       <c r="E12" s="2">
         <v>15.16</v>
       </c>
-      <c r="F12" s="1">
-        <v>25.6</v>
+      <c r="F12" s="2">
+        <v>0.25600000000000001</v>
       </c>
       <c r="G12" s="2">
         <v>1.988</v>
@@ -854,8 +854,8 @@
       <c r="E13" s="2">
         <v>15.859999999999996</v>
       </c>
-      <c r="F13" s="1">
-        <v>23.4</v>
+      <c r="F13" s="2">
+        <v>0.23399999999999999</v>
       </c>
       <c r="G13" s="2">
         <v>1.8560000000000003</v>
@@ -880,8 +880,8 @@
       <c r="E14" s="2">
         <v>13.5</v>
       </c>
-      <c r="F14" s="1">
-        <v>22</v>
+      <c r="F14" s="2">
+        <v>0.22</v>
       </c>
       <c r="G14" s="2">
         <v>1.95</v>
@@ -906,8 +906,8 @@
       <c r="E15" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F15" s="1">
-        <v>21.2</v>
+      <c r="F15" s="2">
+        <v>0.21199999999999999</v>
       </c>
       <c r="G15" s="2">
         <v>1.304</v>
@@ -932,8 +932,8 @@
       <c r="E16" s="2">
         <v>22.32</v>
       </c>
-      <c r="F16" s="1">
-        <v>30</v>
+      <c r="F16" s="2">
+        <v>0.3</v>
       </c>
       <c r="G16" s="2">
         <v>2.0379999999999998</v>
@@ -958,8 +958,8 @@
       <c r="E17" s="2">
         <v>18.36</v>
       </c>
-      <c r="F17" s="1">
-        <v>20</v>
+      <c r="F17" s="2">
+        <v>0.2</v>
       </c>
       <c r="G17" s="2">
         <v>0.71599999999999997</v>
@@ -984,8 +984,8 @@
       <c r="E18" s="2">
         <v>13.36</v>
       </c>
-      <c r="F18" s="1">
-        <v>58.2</v>
+      <c r="F18" s="2">
+        <v>0.58200000000000007</v>
       </c>
       <c r="G18" s="2">
         <v>0.752</v>
@@ -1010,8 +1010,8 @@
       <c r="E19" s="2">
         <v>16.600000000000001</v>
       </c>
-      <c r="F19" s="1">
-        <v>37.5</v>
+      <c r="F19" s="2">
+        <v>0.375</v>
       </c>
       <c r="G19" s="2">
         <v>0.89500000000000002</v>
@@ -1036,8 +1036,8 @@
       <c r="E20" s="2">
         <v>14</v>
       </c>
-      <c r="F20" s="1">
-        <v>24</v>
+      <c r="F20" s="2">
+        <v>0.24</v>
       </c>
       <c r="G20" s="2">
         <v>1.0925</v>
@@ -1062,8 +1062,8 @@
       <c r="E21" s="2">
         <v>10.739999999999998</v>
       </c>
-      <c r="F21" s="1">
-        <v>53.4</v>
+      <c r="F21" s="2">
+        <v>0.53400000000000003</v>
       </c>
       <c r="G21" s="2">
         <v>0.39600000000000002</v>
@@ -1088,8 +1088,8 @@
       <c r="E22" s="2">
         <v>7.76</v>
       </c>
-      <c r="F22" s="1">
-        <v>17.2</v>
+      <c r="F22" s="2">
+        <v>0.17199999999999999</v>
       </c>
       <c r="G22" s="2">
         <v>0.8</v>
@@ -1114,8 +1114,8 @@
       <c r="E23" s="2">
         <v>19.2</v>
       </c>
-      <c r="F23" s="1">
-        <v>26.6</v>
+      <c r="F23" s="2">
+        <v>0.26600000000000001</v>
       </c>
       <c r="G23" s="2">
         <v>0.56600000000000006</v>
@@ -1140,8 +1140,8 @@
       <c r="E24" s="2">
         <v>15.419999999999998</v>
       </c>
-      <c r="F24" s="1">
-        <v>43.8</v>
+      <c r="F24" s="2">
+        <v>0.43799999999999994</v>
       </c>
       <c r="G24" s="2">
         <v>0.42000000000000004</v>
@@ -1166,8 +1166,8 @@
       <c r="E25" s="2">
         <v>15</v>
       </c>
-      <c r="F25" s="1">
-        <v>3</v>
+      <c r="F25" s="2">
+        <v>0.03</v>
       </c>
       <c r="G25" s="2">
         <v>0.625</v>
@@ -1192,8 +1192,8 @@
       <c r="E26" s="2">
         <v>8.9</v>
       </c>
-      <c r="F26" s="1">
-        <v>34.200000000000003</v>
+      <c r="F26" s="2">
+        <v>0.34200000000000003</v>
       </c>
       <c r="G26" s="2">
         <v>0.20400000000000001</v>
@@ -1218,8 +1218,8 @@
       <c r="E27" s="2">
         <v>15.819999999999999</v>
       </c>
-      <c r="F27" s="1">
-        <v>24.4</v>
+      <c r="F27" s="2">
+        <v>0.24399999999999999</v>
       </c>
       <c r="G27" s="2">
         <v>0.61199999999999999</v>
@@ -1244,8 +1244,8 @@
       <c r="E28" s="2">
         <v>12.2</v>
       </c>
-      <c r="F28" s="1">
-        <v>11</v>
+      <c r="F28" s="2">
+        <v>0.11</v>
       </c>
       <c r="G28" s="2">
         <v>0.91500000000000004</v>
@@ -1270,8 +1270,8 @@
       <c r="E29" s="2">
         <v>6.4599999999999991</v>
       </c>
-      <c r="F29" s="1">
-        <v>7.6</v>
+      <c r="F29" s="2">
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="G29" s="2">
         <v>0.62600000000000011</v>
@@ -1296,8 +1296,8 @@
       <c r="E30" s="2">
         <v>8.42</v>
       </c>
-      <c r="F30" s="1">
-        <v>7.8</v>
+      <c r="F30" s="2">
+        <v>7.8E-2</v>
       </c>
       <c r="G30" s="2">
         <v>1.002</v>
@@ -1322,8 +1322,8 @@
       <c r="E31" s="2">
         <v>13.34</v>
       </c>
-      <c r="F31" s="1">
-        <v>5</v>
+      <c r="F31" s="2">
+        <v>0.05</v>
       </c>
       <c r="G31" s="2">
         <v>0.69399999999999995</v>
@@ -1331,6 +1331,9 @@
       <c r="H31" s="1">
         <v>4</v>
       </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F32" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/total_parcelas.xlsx
+++ b/total_parcelas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6406CAA5-A9A8-4C66-B0F9-512E34AFF4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67BD0E02-66EF-4B7B-A150-D7FF19B88294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{326D8460-CF33-46E7-A7F9-8315620B1DD2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>sample</t>
   </si>
@@ -150,6 +150,18 @@
   </si>
   <si>
     <t>V_hu</t>
+  </si>
+  <si>
+    <t>T_den</t>
+  </si>
+  <si>
+    <t>T_fue</t>
+  </si>
+  <si>
+    <t>H_den</t>
+  </si>
+  <si>
+    <t>H_fue</t>
   </si>
 </sst>
 </file>
@@ -523,36 +535,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE44BCBA-D928-4EB0-BB70-EF020CEEAF2E}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -560,25 +584,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="D2" s="2">
+        <v>23.64</v>
+      </c>
+      <c r="E2" s="2">
+        <v>60.739999999999995</v>
+      </c>
+      <c r="F2" s="2">
+        <v>60.840000000000011</v>
+      </c>
+      <c r="G2" s="2">
         <v>0.14000000000000057</v>
       </c>
-      <c r="D2" s="2">
+      <c r="H2" s="2">
         <v>0.10000000000001563</v>
       </c>
-      <c r="E2" s="2">
+      <c r="I2" s="2">
         <v>14.86</v>
       </c>
-      <c r="F2" s="2">
+      <c r="J2" s="2">
         <v>0.18</v>
       </c>
-      <c r="G2" s="2">
+      <c r="K2" s="2">
         <v>1.4339999999999999</v>
       </c>
-      <c r="H2">
+      <c r="L2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -586,25 +622,37 @@
         <v>1</v>
       </c>
       <c r="C3" s="2">
+        <v>29.216666666666669</v>
+      </c>
+      <c r="D3" s="2">
+        <v>29.240000000000006</v>
+      </c>
+      <c r="E3" s="2">
+        <v>48.906666666666673</v>
+      </c>
+      <c r="F3" s="2">
+        <v>49.473333333333336</v>
+      </c>
+      <c r="G3" s="2">
         <v>2.3333333333336981E-2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="H3" s="2">
         <v>0.56666666666666288</v>
       </c>
-      <c r="E3" s="2">
+      <c r="I3" s="2">
         <v>10.393333333333333</v>
       </c>
-      <c r="F3" s="2">
+      <c r="J3" s="2">
         <v>0.34</v>
       </c>
-      <c r="G3" s="2">
+      <c r="K3" s="2">
         <v>2.254</v>
       </c>
-      <c r="H3">
+      <c r="L3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -612,25 +660,37 @@
         <v>1</v>
       </c>
       <c r="C4" s="2">
+        <v>28.259999999999998</v>
+      </c>
+      <c r="D4" s="2">
+        <v>28.420000000000005</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50.86</v>
+      </c>
+      <c r="F4" s="2">
+        <v>50.46</v>
+      </c>
+      <c r="G4" s="2">
         <v>0.16000000000000725</v>
       </c>
-      <c r="D4" s="2">
+      <c r="H4" s="2">
         <v>0.39999999999999858</v>
       </c>
-      <c r="E4" s="2">
+      <c r="I4" s="2">
         <v>16.02</v>
       </c>
-      <c r="F4" s="2">
+      <c r="J4" s="2">
         <v>0.20600000000000002</v>
       </c>
-      <c r="G4" s="2">
+      <c r="K4" s="2">
         <v>2.0140000000000002</v>
       </c>
-      <c r="H4">
+      <c r="L4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -638,25 +698,37 @@
         <v>1</v>
       </c>
       <c r="C5" s="2">
+        <v>25.98</v>
+      </c>
+      <c r="D5" s="2">
+        <v>26.04</v>
+      </c>
+      <c r="E5" s="2">
+        <v>54.820000000000007</v>
+      </c>
+      <c r="F5" s="2">
+        <v>55.4</v>
+      </c>
+      <c r="G5" s="2">
         <v>5.9999999999998721E-2</v>
       </c>
-      <c r="D5" s="2">
+      <c r="H5" s="2">
         <v>0.57999999999999119</v>
       </c>
-      <c r="E5" s="2">
+      <c r="I5" s="2">
         <v>20.04</v>
       </c>
-      <c r="F5" s="2">
+      <c r="J5" s="2">
         <v>0.34</v>
       </c>
-      <c r="G5" s="2">
+      <c r="K5" s="2">
         <v>2.742</v>
       </c>
-      <c r="H5">
+      <c r="L5">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -664,25 +736,37 @@
         <v>1</v>
       </c>
       <c r="C6" s="2">
+        <v>32.040000000000006</v>
+      </c>
+      <c r="D6" s="2">
+        <v>32.179999999999993</v>
+      </c>
+      <c r="E6" s="2">
+        <v>51.160000000000004</v>
+      </c>
+      <c r="F6" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="G6" s="2">
         <v>0.13999999999998636</v>
       </c>
-      <c r="D6" s="2">
+      <c r="H6" s="2">
         <v>1.3399999999999963</v>
       </c>
-      <c r="E6" s="2">
+      <c r="I6" s="2">
         <v>11.04</v>
       </c>
-      <c r="F6" s="2">
+      <c r="J6" s="2">
         <v>0.222</v>
       </c>
-      <c r="G6" s="2">
+      <c r="K6" s="2">
         <v>1.21</v>
       </c>
-      <c r="H6">
+      <c r="L6">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -690,25 +774,37 @@
         <v>1</v>
       </c>
       <c r="C7" s="2">
+        <v>29.179999999999996</v>
+      </c>
+      <c r="D7" s="2">
+        <v>29.160000000000004</v>
+      </c>
+      <c r="E7" s="2">
+        <v>50.56</v>
+      </c>
+      <c r="F7" s="2">
+        <v>48.280000000000008</v>
+      </c>
+      <c r="G7" s="2">
         <v>1.9999999999992468E-2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="H7" s="2">
         <v>2.279999999999994</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>9.36</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>0.222</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>1.5779999999999998</v>
       </c>
-      <c r="H7">
+      <c r="L7">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -716,25 +812,37 @@
         <v>1</v>
       </c>
       <c r="C8" s="2">
+        <v>32.6</v>
+      </c>
+      <c r="D8" s="2">
+        <v>32.65</v>
+      </c>
+      <c r="E8" s="2">
+        <v>40.774999999999999</v>
+      </c>
+      <c r="F8" s="2">
+        <v>41.05</v>
+      </c>
+      <c r="G8" s="2">
         <v>4.9999999999997158E-2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="H8" s="2">
         <v>0.27499999999999858</v>
       </c>
-      <c r="E8" s="2">
+      <c r="I8" s="2">
         <v>9.125</v>
       </c>
-      <c r="F8" s="2">
+      <c r="J8" s="2">
         <v>0.155</v>
       </c>
-      <c r="G8" s="2">
+      <c r="K8" s="2">
         <v>1.7674999999999998</v>
       </c>
-      <c r="H8">
+      <c r="L8">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -742,25 +850,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="2">
+        <v>30.339999999999996</v>
+      </c>
+      <c r="D9" s="2">
+        <v>30.46</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>44.900000000000006</v>
+      </c>
+      <c r="G9" s="2">
         <v>0.12000000000000455</v>
       </c>
-      <c r="D9" s="2">
+      <c r="H9" s="2">
         <v>1.5999999999999943</v>
       </c>
-      <c r="E9" s="2">
+      <c r="I9" s="2">
         <v>8.16</v>
       </c>
-      <c r="F9" s="2">
+      <c r="J9" s="2">
         <v>0.28199999999999997</v>
       </c>
-      <c r="G9" s="2">
+      <c r="K9" s="2">
         <v>1.92</v>
       </c>
-      <c r="H9">
+      <c r="L9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -768,25 +888,37 @@
         <v>1</v>
       </c>
       <c r="C10" s="2">
+        <v>31.674999999999997</v>
+      </c>
+      <c r="D10" s="2">
+        <v>31.824999999999999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>51.949999999999996</v>
+      </c>
+      <c r="F10" s="2">
+        <v>51.974999999999994</v>
+      </c>
+      <c r="G10" s="2">
         <v>0.15000000000000213</v>
       </c>
-      <c r="D10" s="2">
+      <c r="H10" s="2">
         <v>2.4999999999998579E-2</v>
       </c>
-      <c r="E10" s="2">
+      <c r="I10" s="2">
         <v>10.074999999999999</v>
       </c>
-      <c r="F10" s="2">
+      <c r="J10" s="2">
         <v>0.34250000000000003</v>
       </c>
-      <c r="G10" s="2">
+      <c r="K10" s="2">
         <v>2.1124999999999998</v>
       </c>
-      <c r="H10">
+      <c r="L10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -794,25 +926,37 @@
         <v>1</v>
       </c>
       <c r="C11" s="2">
+        <v>33.75</v>
+      </c>
+      <c r="D11" s="2">
+        <v>33.725000000000001</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46.924999999999997</v>
+      </c>
+      <c r="F11" s="2">
+        <v>49.174999999999997</v>
+      </c>
+      <c r="G11" s="2">
         <v>2.4999999999998579E-2</v>
       </c>
-      <c r="D11" s="2">
+      <c r="H11" s="2">
         <v>2.25</v>
       </c>
-      <c r="E11" s="2">
+      <c r="I11" s="2">
         <v>6.3999999999999995</v>
       </c>
-      <c r="F11" s="2">
+      <c r="J11" s="2">
         <v>0.33</v>
       </c>
-      <c r="G11" s="2">
+      <c r="K11" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H11">
+      <c r="L11">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -820,25 +964,37 @@
         <v>1</v>
       </c>
       <c r="C12" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>31.320000000000004</v>
+      </c>
+      <c r="E12" s="2">
+        <v>48.18</v>
+      </c>
+      <c r="F12" s="2">
+        <v>47.62</v>
+      </c>
+      <c r="G12" s="2">
         <v>1.8200000000000038</v>
       </c>
-      <c r="D12" s="2">
+      <c r="H12" s="2">
         <v>0.56000000000000227</v>
       </c>
-      <c r="E12" s="2">
+      <c r="I12" s="2">
         <v>15.16</v>
       </c>
-      <c r="F12" s="2">
+      <c r="J12" s="2">
         <v>0.25600000000000001</v>
       </c>
-      <c r="G12" s="2">
+      <c r="K12" s="2">
         <v>1.988</v>
       </c>
-      <c r="H12">
+      <c r="L12">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -846,25 +1002,37 @@
         <v>1</v>
       </c>
       <c r="C13" s="2">
+        <v>23.54</v>
+      </c>
+      <c r="D13" s="2">
+        <v>23.62</v>
+      </c>
+      <c r="E13" s="2">
+        <v>62.260000000000005</v>
+      </c>
+      <c r="F13" s="2">
+        <v>62.279999999999994</v>
+      </c>
+      <c r="G13" s="2">
         <v>8.0000000000001847E-2</v>
       </c>
-      <c r="D13" s="2">
+      <c r="H13" s="2">
         <v>1.9999999999988916E-2</v>
       </c>
-      <c r="E13" s="2">
+      <c r="I13" s="2">
         <v>15.859999999999996</v>
       </c>
-      <c r="F13" s="2">
+      <c r="J13" s="2">
         <v>0.23399999999999999</v>
       </c>
-      <c r="G13" s="2">
+      <c r="K13" s="2">
         <v>1.8560000000000003</v>
       </c>
-      <c r="H13">
+      <c r="L13">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -872,25 +1040,37 @@
         <v>1</v>
       </c>
       <c r="C14" s="2">
+        <v>29.7</v>
+      </c>
+      <c r="D14" s="2">
+        <v>29.6</v>
+      </c>
+      <c r="E14" s="2">
+        <v>47.4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46.9</v>
+      </c>
+      <c r="G14" s="2">
         <v>9.9999999999997868E-2</v>
       </c>
-      <c r="D14" s="2">
+      <c r="H14" s="2">
         <v>0.5</v>
       </c>
-      <c r="E14" s="2">
+      <c r="I14" s="2">
         <v>13.5</v>
       </c>
-      <c r="F14" s="2">
+      <c r="J14" s="2">
         <v>0.22</v>
       </c>
-      <c r="G14" s="2">
+      <c r="K14" s="2">
         <v>1.95</v>
       </c>
-      <c r="H14">
+      <c r="L14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -898,25 +1078,37 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
+        <v>33.059999999999995</v>
+      </c>
+      <c r="D15" s="2">
+        <v>32.36</v>
+      </c>
+      <c r="E15" s="2">
+        <v>49.320000000000007</v>
+      </c>
+      <c r="F15" s="2">
+        <v>50</v>
+      </c>
+      <c r="G15" s="2">
         <v>0.69999999999999574</v>
       </c>
-      <c r="D15" s="2">
+      <c r="H15" s="2">
         <v>0.67999999999999261</v>
       </c>
-      <c r="E15" s="2">
+      <c r="I15" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F15" s="2">
+      <c r="J15" s="2">
         <v>0.21199999999999999</v>
       </c>
-      <c r="G15" s="2">
+      <c r="K15" s="2">
         <v>1.304</v>
       </c>
-      <c r="H15">
+      <c r="L15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -924,25 +1116,37 @@
         <v>1</v>
       </c>
       <c r="C16" s="2">
+        <v>24.18</v>
+      </c>
+      <c r="D16" s="2">
+        <v>24.48</v>
+      </c>
+      <c r="E16" s="2">
+        <v>58.820000000000007</v>
+      </c>
+      <c r="F16" s="2">
+        <v>57.86</v>
+      </c>
+      <c r="G16" s="2">
         <v>0.30000000000000071</v>
       </c>
-      <c r="D16" s="2">
+      <c r="H16" s="2">
         <v>0.96000000000000796</v>
       </c>
-      <c r="E16" s="2">
+      <c r="I16" s="2">
         <v>22.32</v>
       </c>
-      <c r="F16" s="2">
+      <c r="J16" s="2">
         <v>0.3</v>
       </c>
-      <c r="G16" s="2">
+      <c r="K16" s="2">
         <v>2.0379999999999998</v>
       </c>
-      <c r="H16">
+      <c r="L16">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -950,25 +1154,37 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
+        <v>23.580000000000002</v>
+      </c>
+      <c r="D17" s="2">
+        <v>27.22</v>
+      </c>
+      <c r="E17" s="2">
+        <v>55.3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>54.1</v>
+      </c>
+      <c r="G17" s="2">
         <v>3.639999999999997</v>
       </c>
-      <c r="D17" s="2">
+      <c r="H17" s="2">
         <v>1.1999999999999957</v>
       </c>
-      <c r="E17" s="2">
+      <c r="I17" s="2">
         <v>18.36</v>
       </c>
-      <c r="F17" s="2">
+      <c r="J17" s="2">
         <v>0.2</v>
       </c>
-      <c r="G17" s="2">
+      <c r="K17" s="2">
         <v>0.71599999999999997</v>
       </c>
-      <c r="H17" s="1">
+      <c r="L17" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -976,25 +1192,37 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
+        <v>23.779999999999998</v>
+      </c>
+      <c r="D18" s="2">
+        <v>27.419999999999998</v>
+      </c>
+      <c r="E18" s="2">
+        <v>52.319999999999993</v>
+      </c>
+      <c r="F18" s="2">
+        <v>51.6</v>
+      </c>
+      <c r="G18" s="2">
         <v>3.6400000000000006</v>
       </c>
-      <c r="D18" s="2">
+      <c r="H18" s="2">
         <v>0.71999999999999176</v>
       </c>
-      <c r="E18" s="2">
+      <c r="I18" s="2">
         <v>13.36</v>
       </c>
-      <c r="F18" s="2">
+      <c r="J18" s="2">
         <v>0.58200000000000007</v>
       </c>
-      <c r="G18" s="2">
+      <c r="K18" s="2">
         <v>0.752</v>
       </c>
-      <c r="H18" s="1">
+      <c r="L18" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1002,25 +1230,37 @@
         <v>0</v>
       </c>
       <c r="C19" s="2">
+        <v>23.924999999999997</v>
+      </c>
+      <c r="D19" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>52.3</v>
+      </c>
+      <c r="F19" s="2">
+        <v>52.174999999999997</v>
+      </c>
+      <c r="G19" s="2">
         <v>3.3750000000000036</v>
       </c>
-      <c r="D19" s="2">
+      <c r="H19" s="2">
         <v>0.125</v>
       </c>
-      <c r="E19" s="2">
+      <c r="I19" s="2">
         <v>16.600000000000001</v>
       </c>
-      <c r="F19" s="2">
+      <c r="J19" s="2">
         <v>0.375</v>
       </c>
-      <c r="G19" s="2">
+      <c r="K19" s="2">
         <v>0.89500000000000002</v>
       </c>
-      <c r="H19" s="1">
+      <c r="L19" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1028,25 +1268,37 @@
         <v>0</v>
       </c>
       <c r="C20" s="2">
+        <v>24.275000000000002</v>
+      </c>
+      <c r="D20" s="2">
+        <v>26.95</v>
+      </c>
+      <c r="E20" s="2">
+        <v>53.2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>53.625</v>
+      </c>
+      <c r="G20" s="2">
         <v>2.6749999999999972</v>
       </c>
-      <c r="D20" s="2">
+      <c r="H20" s="2">
         <v>0.42499999999999716</v>
       </c>
-      <c r="E20" s="2">
+      <c r="I20" s="2">
         <v>14</v>
       </c>
-      <c r="F20" s="2">
+      <c r="J20" s="2">
         <v>0.24</v>
       </c>
-      <c r="G20" s="2">
+      <c r="K20" s="2">
         <v>1.0925</v>
       </c>
-      <c r="H20" s="1">
+      <c r="L20" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1054,25 +1306,37 @@
         <v>0</v>
       </c>
       <c r="C21" s="2">
+        <v>24.339999999999996</v>
+      </c>
+      <c r="D21" s="2">
+        <v>27.020000000000003</v>
+      </c>
+      <c r="E21" s="2">
+        <v>52.160000000000004</v>
+      </c>
+      <c r="F21" s="2">
+        <v>52.14</v>
+      </c>
+      <c r="G21" s="2">
         <v>2.6800000000000068</v>
       </c>
-      <c r="D21" s="2">
+      <c r="H21" s="2">
         <v>2.0000000000003126E-2</v>
       </c>
-      <c r="E21" s="2">
+      <c r="I21" s="2">
         <v>10.739999999999998</v>
       </c>
-      <c r="F21" s="2">
+      <c r="J21" s="2">
         <v>0.53400000000000003</v>
       </c>
-      <c r="G21" s="2">
+      <c r="K21" s="2">
         <v>0.39600000000000002</v>
       </c>
-      <c r="H21" s="1">
+      <c r="L21" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1080,25 +1344,37 @@
         <v>0</v>
       </c>
       <c r="C22" s="2">
+        <v>24.04</v>
+      </c>
+      <c r="D22" s="2">
+        <v>26.740000000000002</v>
+      </c>
+      <c r="E22" s="2">
+        <v>53.56</v>
+      </c>
+      <c r="F22" s="2">
+        <v>53.839999999999996</v>
+      </c>
+      <c r="G22" s="2">
         <v>2.7000000000000028</v>
       </c>
-      <c r="D22" s="2">
+      <c r="H22" s="2">
         <v>0.27999999999999403</v>
       </c>
-      <c r="E22" s="2">
+      <c r="I22" s="2">
         <v>7.76</v>
       </c>
-      <c r="F22" s="2">
+      <c r="J22" s="2">
         <v>0.17199999999999999</v>
       </c>
-      <c r="G22" s="2">
+      <c r="K22" s="2">
         <v>0.8</v>
       </c>
-      <c r="H22" s="1">
+      <c r="L22" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1106,25 +1382,37 @@
         <v>0</v>
       </c>
       <c r="C23" s="2">
+        <v>22.32</v>
+      </c>
+      <c r="D23" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="E23" s="2">
+        <v>61.42</v>
+      </c>
+      <c r="F23" s="2">
+        <v>60.7</v>
+      </c>
+      <c r="G23" s="2">
         <v>2.120000000000001</v>
       </c>
-      <c r="D23" s="2">
+      <c r="H23" s="2">
         <v>0.71999999999999886</v>
       </c>
-      <c r="E23" s="2">
+      <c r="I23" s="2">
         <v>19.2</v>
       </c>
-      <c r="F23" s="2">
+      <c r="J23" s="2">
         <v>0.26600000000000001</v>
       </c>
-      <c r="G23" s="2">
+      <c r="K23" s="2">
         <v>0.56600000000000006</v>
       </c>
-      <c r="H23" s="1">
+      <c r="L23" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1132,25 +1420,37 @@
         <v>0</v>
       </c>
       <c r="C24" s="2">
+        <v>23</v>
+      </c>
+      <c r="D24" s="2">
+        <v>25.619999999999997</v>
+      </c>
+      <c r="E24" s="2">
+        <v>57.8</v>
+      </c>
+      <c r="F24" s="2">
+        <v>57.56</v>
+      </c>
+      <c r="G24" s="2">
         <v>2.6199999999999974</v>
       </c>
-      <c r="D24" s="2">
+      <c r="H24" s="2">
         <v>0.23999999999999488</v>
       </c>
-      <c r="E24" s="2">
+      <c r="I24" s="2">
         <v>15.419999999999998</v>
       </c>
-      <c r="F24" s="2">
+      <c r="J24" s="2">
         <v>0.43799999999999994</v>
       </c>
-      <c r="G24" s="2">
+      <c r="K24" s="2">
         <v>0.42000000000000004</v>
       </c>
-      <c r="H24" s="1">
+      <c r="L24" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1158,25 +1458,37 @@
         <v>0</v>
       </c>
       <c r="C25" s="2">
+        <v>23.15</v>
+      </c>
+      <c r="D25" s="2">
+        <v>26.85</v>
+      </c>
+      <c r="E25" s="2">
+        <v>54.45</v>
+      </c>
+      <c r="F25" s="2">
+        <v>54.55</v>
+      </c>
+      <c r="G25" s="2">
         <v>3.7000000000000028</v>
       </c>
-      <c r="D25" s="2">
+      <c r="H25" s="2">
         <v>9.9999999999994316E-2</v>
       </c>
-      <c r="E25" s="2">
+      <c r="I25" s="2">
         <v>15</v>
       </c>
-      <c r="F25" s="2">
+      <c r="J25" s="2">
         <v>0.03</v>
       </c>
-      <c r="G25" s="2">
+      <c r="K25" s="2">
         <v>0.625</v>
       </c>
-      <c r="H25" s="1">
+      <c r="L25" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1184,25 +1496,37 @@
         <v>0</v>
       </c>
       <c r="C26" s="2">
+        <v>24.080000000000002</v>
+      </c>
+      <c r="D26" s="2">
+        <v>25.639999999999997</v>
+      </c>
+      <c r="E26" s="2">
+        <v>56.98</v>
+      </c>
+      <c r="F26" s="2">
+        <v>57.040000000000006</v>
+      </c>
+      <c r="G26" s="2">
         <v>1.5599999999999952</v>
       </c>
-      <c r="D26" s="2">
+      <c r="H26" s="2">
         <v>6.0000000000009379E-2</v>
       </c>
-      <c r="E26" s="2">
+      <c r="I26" s="2">
         <v>8.9</v>
       </c>
-      <c r="F26" s="2">
+      <c r="J26" s="2">
         <v>0.34200000000000003</v>
       </c>
-      <c r="G26" s="2">
+      <c r="K26" s="2">
         <v>0.20400000000000001</v>
       </c>
-      <c r="H26" s="1">
+      <c r="L26" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1210,25 +1534,37 @@
         <v>0</v>
       </c>
       <c r="C27" s="2">
+        <v>22.7</v>
+      </c>
+      <c r="D27" s="2">
+        <v>25.479999999999997</v>
+      </c>
+      <c r="E27" s="2">
+        <v>58.42</v>
+      </c>
+      <c r="F27" s="2">
+        <v>58.08</v>
+      </c>
+      <c r="G27" s="2">
         <v>2.7799999999999976</v>
       </c>
-      <c r="D27" s="2">
+      <c r="H27" s="2">
         <v>0.34000000000000341</v>
       </c>
-      <c r="E27" s="2">
+      <c r="I27" s="2">
         <v>15.819999999999999</v>
       </c>
-      <c r="F27" s="2">
+      <c r="J27" s="2">
         <v>0.24399999999999999</v>
       </c>
-      <c r="G27" s="2">
+      <c r="K27" s="2">
         <v>0.61199999999999999</v>
       </c>
-      <c r="H27" s="1">
+      <c r="L27" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1236,25 +1572,37 @@
         <v>0</v>
       </c>
       <c r="C28" s="2">
+        <v>23.75</v>
+      </c>
+      <c r="D28" s="2">
+        <v>26.75</v>
+      </c>
+      <c r="E28" s="2">
+        <v>53.7</v>
+      </c>
+      <c r="F28" s="2">
+        <v>53.95</v>
+      </c>
+      <c r="G28" s="2">
         <v>3</v>
       </c>
-      <c r="D28" s="2">
+      <c r="H28" s="2">
         <v>0.25</v>
       </c>
-      <c r="E28" s="2">
+      <c r="I28" s="2">
         <v>12.2</v>
       </c>
-      <c r="F28" s="2">
+      <c r="J28" s="2">
         <v>0.11</v>
       </c>
-      <c r="G28" s="2">
+      <c r="K28" s="2">
         <v>0.91500000000000004</v>
       </c>
-      <c r="H28" s="1">
+      <c r="L28" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1262,25 +1610,37 @@
         <v>0</v>
       </c>
       <c r="C29" s="2">
+        <v>31.920000000000005</v>
+      </c>
+      <c r="D29" s="2">
+        <v>31.52</v>
+      </c>
+      <c r="E29" s="2">
+        <v>50.08</v>
+      </c>
+      <c r="F29" s="2">
+        <v>50.04</v>
+      </c>
+      <c r="G29" s="2">
         <v>0.40000000000000568</v>
       </c>
-      <c r="D29" s="2">
+      <c r="H29" s="2">
         <v>3.9999999999999147E-2</v>
       </c>
-      <c r="E29" s="2">
+      <c r="I29" s="2">
         <v>6.4599999999999991</v>
       </c>
-      <c r="F29" s="2">
+      <c r="J29" s="2">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="G29" s="2">
+      <c r="K29" s="2">
         <v>0.62600000000000011</v>
       </c>
-      <c r="H29" s="1">
+      <c r="L29" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1288,25 +1648,37 @@
         <v>0</v>
       </c>
       <c r="C30" s="2">
+        <v>29.380000000000003</v>
+      </c>
+      <c r="D30" s="2">
+        <v>29.54</v>
+      </c>
+      <c r="E30" s="2">
+        <v>55.019999999999996</v>
+      </c>
+      <c r="F30" s="2">
+        <v>55.220000000000006</v>
+      </c>
+      <c r="G30" s="2">
         <v>0.15999999999999659</v>
       </c>
-      <c r="D30" s="2">
+      <c r="H30" s="2">
         <v>0.20000000000000995</v>
       </c>
-      <c r="E30" s="2">
+      <c r="I30" s="2">
         <v>8.42</v>
       </c>
-      <c r="F30" s="2">
+      <c r="J30" s="2">
         <v>7.8E-2</v>
       </c>
-      <c r="G30" s="2">
+      <c r="K30" s="2">
         <v>1.002</v>
       </c>
-      <c r="H30" s="1">
+      <c r="L30" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1314,26 +1686,35 @@
         <v>0</v>
       </c>
       <c r="C31" s="2">
+        <v>33.58</v>
+      </c>
+      <c r="D31" s="2">
+        <v>33.559999999999988</v>
+      </c>
+      <c r="E31" s="2">
+        <v>47.620000000000005</v>
+      </c>
+      <c r="F31" s="2">
+        <v>46.82</v>
+      </c>
+      <c r="G31" s="2">
         <v>2.0000000000010232E-2</v>
       </c>
-      <c r="D31" s="2">
+      <c r="H31" s="2">
         <v>0.80000000000000426</v>
       </c>
-      <c r="E31" s="2">
+      <c r="I31" s="2">
         <v>13.34</v>
       </c>
-      <c r="F31" s="2">
+      <c r="J31" s="2">
         <v>0.05</v>
       </c>
-      <c r="G31" s="2">
+      <c r="K31" s="2">
         <v>0.69399999999999995</v>
       </c>
-      <c r="H31" s="1">
+      <c r="L31" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F32" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
